--- a/Config/Datas/rune.xlsx
+++ b/Config/Datas/rune.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="rune_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="rune_upgrade_info" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -16,14 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -478,149 +472,149 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1038,16 +1032,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="17.5" customWidth="1" min="2" max="3"/>
+    <col width="19.125" customWidth="1" min="2" max="2"/>
+    <col width="17.5" customWidth="1" min="3" max="3"/>
     <col width="23.125" customWidth="1" min="4" max="4"/>
     <col width="12.875" customWidth="1" min="5" max="5"/>
     <col width="18.5" customWidth="1" min="6" max="6"/>
     <col width="17.5" customWidth="1" min="7" max="7"/>
     <col width="16.25" customWidth="1" min="8" max="8"/>
-    <col width="18.875" customWidth="1" min="11" max="11"/>
+    <col width="28.375" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1229,12 +1224,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>rune_perm_map</t>
+          <t>common_lamp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>地图</t>
+          <t>灯/基础</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1248,23 +1243,21 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>unlock_world_map</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>地图符文</t>
+          <t>灯</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>获得后解锁世界地图相关功能</t>
+          <t>初始永久符文，升级项在 rune_upgrade_info</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1292,6 +1285,14 @@
           <t>None</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>丰饶</t>
@@ -1299,17 +1300,69 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>获得植物亲和能力</t>
+          <t>植物亲和基础符文</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rune_lady</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>淑女</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Equippable</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>player_naishou_to_jianshang</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>耐受核心</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>核心槽装配符文</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>rune_core_naishou</t>
+          <t>rune_evil_hand</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>淫邪手部</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1319,37 +1372,44 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Hand</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>player_naishou_to_jianshang</t>
+          <t>queen_desire_charm_01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>0</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>耐受核心</t>
+          <t>魅惑之手</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>装配后获得耐受减伤被动</t>
+          <t>手部槽装配符文</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>rune_hand_charm</t>
+          <t>rune_foot_spirit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>灵体之足</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1359,71 +1419,566 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Foot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>queen_desire_charm_01</t>
+          <t>h_spirit_immune</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>0</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>魅惑之手</t>
+          <t>灵体之足</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>装配后获得魅惑相关被动</t>
+          <t>足部槽装配符文</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="17.25" customWidth="1" min="2" max="2"/>
+    <col width="30.75" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>upgrade_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>base_rune_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>branch_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prerequisite_upgrade_ids</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>passive_skill_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>func_unlock_key</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>func_open_type</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EFuncOpenType</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lamp_a_map</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>灯A-地图</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>common_lamp</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>unlock_world_map</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>灯·A·地图</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>解锁世界地图功能</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lamp_a_sense</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>灯A-感知</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>common_lamp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lamp_a_map</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>灯·A·感知</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>依赖地图分支的二级升级</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lamp_b_travel</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>灯B-旅行</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>common_lamp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>灯·B·旅行</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>解锁旅行相关功能</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lamp_b_fast</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>灯B-疾行</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>common_lamp</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>lamp_b_travel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>灯·B·疾行</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>旅行分支二级升级</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lamp_c_harvest</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>灯C-丰饶</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>common_lamp</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>player_harvest_green</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>灯·C·丰饶</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>获得植物亲和被动</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>rune_foot_spirit</t>
+          <t>harvest_green_basic</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>丰饶基础</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Equippable</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Foot</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>h_spirit_immune</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>灵体之足</t>
-        </is>
-      </c>
+          <t>harvest_green</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>player_harvest_green</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>装配后获得灵体免疫被动</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>22</v>
+          <t>丰饶·基础</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>强化植物亲和</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>harvest_green_plus</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>丰饶进阶</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>harvest_green</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>harvest_green_basic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>丰饶·进阶</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>需先解锁基础</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/rune.xlsx
+++ b/Config/Datas/rune.xlsx
@@ -1468,7 +1468,7 @@
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J7" t="s">
         <v>37</v>

--- a/Config/Datas/rune.xlsx
+++ b/Config/Datas/rune.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="rune_data" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/rune.xlsx
+++ b/Config/Datas/rune.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="rune_data" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -42,6 +42,9 @@
     <t>##comment</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>rune_type</t>
   </si>
   <si>
@@ -57,153 +60,141 @@
     <t>icon</t>
   </si>
   <si>
-    <t>desc</t>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>ERuneType</t>
+  </si>
+  <si>
+    <t>ERuneEquipSlot</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>rune_lamp</t>
+  </si>
+  <si>
+    <t>灯</t>
+  </si>
+  <si>
+    <t>旅者的印记。</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>lamp_basic</t>
+  </si>
+  <si>
+    <t>RuneLayout_Lamp</t>
+  </si>
+  <si>
+    <t>rune_harvest</t>
+  </si>
+  <si>
+    <t>丰饶</t>
+  </si>
+  <si>
+    <t>丰饶的印记。</t>
+  </si>
+  <si>
+    <t>harvest_basic</t>
+  </si>
+  <si>
+    <t>RuneLayout_Linear3</t>
+  </si>
+  <si>
+    <t>rune_lady</t>
+  </si>
+  <si>
+    <t>淑女</t>
+  </si>
+  <si>
+    <t>时间尽头的淑女。</t>
+  </si>
+  <si>
+    <t>Equippable</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>lady_initial</t>
+  </si>
+  <si>
+    <t>RuneLayout_Single1</t>
+  </si>
+  <si>
+    <t>rune_evil_hand</t>
+  </si>
+  <si>
+    <t>魅惑之手</t>
+  </si>
+  <si>
+    <t>淫邪手部</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>evil_hand_initial</t>
+  </si>
+  <si>
+    <t>rune_foot_spirit</t>
+  </si>
+  <si>
+    <t>灵体之足</t>
+  </si>
+  <si>
+    <t>Foot</t>
+  </si>
+  <si>
+    <t>foot_spirit_initial</t>
+  </si>
+  <si>
+    <t>upgrade_id</t>
+  </si>
+  <si>
+    <t>base_rune_id</t>
+  </si>
+  <si>
+    <t>prerequisite_upgrade_ids</t>
+  </si>
+  <si>
+    <t>passive_skill_id</t>
+  </si>
+  <si>
+    <t>func_unlock_key</t>
+  </si>
+  <si>
+    <t>func_open_type</t>
+  </si>
+  <si>
+    <t>layout_slot</t>
   </si>
   <si>
     <t>sort_order</t>
   </si>
   <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>ERuneType</t>
-  </si>
-  <si>
-    <t>ERuneEquipSlot</t>
+    <t>(list#sep=|),string</t>
+  </si>
+  <si>
+    <t>EFuncOpenType</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>rune_lamp</t>
-  </si>
-  <si>
-    <t>灯</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>lamp_basic</t>
-  </si>
-  <si>
-    <t>RuneLayout_Lamp</t>
-  </si>
-  <si>
-    <t>初始永久符文，升级项在 rune_upgrade_info</t>
-  </si>
-  <si>
-    <t>rune_harvest</t>
-  </si>
-  <si>
-    <t>丰饶</t>
-  </si>
-  <si>
-    <t>harvest_basic</t>
-  </si>
-  <si>
-    <t>RuneLayout_Linear3</t>
-  </si>
-  <si>
-    <t>植物亲和基础符文</t>
-  </si>
-  <si>
-    <t>rune_lady</t>
-  </si>
-  <si>
-    <t>耐受核心</t>
-  </si>
-  <si>
-    <t>淑女</t>
-  </si>
-  <si>
-    <t>Equippable</t>
-  </si>
-  <si>
-    <t>Core</t>
-  </si>
-  <si>
-    <t>lady_initial</t>
-  </si>
-  <si>
-    <t>RuneLayout_Single1</t>
-  </si>
-  <si>
-    <t>核心槽装配符文</t>
-  </si>
-  <si>
-    <t>rune_evil_hand</t>
-  </si>
-  <si>
-    <t>魅惑之手</t>
-  </si>
-  <si>
-    <t>淫邪手部</t>
-  </si>
-  <si>
-    <t>Hand</t>
-  </si>
-  <si>
-    <t>evil_hand_initial</t>
-  </si>
-  <si>
-    <t>手部槽装配符文</t>
-  </si>
-  <si>
-    <t>rune_foot_spirit</t>
-  </si>
-  <si>
-    <t>灵体之足</t>
-  </si>
-  <si>
-    <t>Foot</t>
-  </si>
-  <si>
-    <t>foot_spirit_initial</t>
-  </si>
-  <si>
-    <t>足部槽装配符文</t>
-  </si>
-  <si>
-    <t>upgrade_id</t>
-  </si>
-  <si>
-    <t>base_rune_id</t>
-  </si>
-  <si>
-    <t>prerequisite_upgrade_ids</t>
-  </si>
-  <si>
-    <t>passive_skill_id</t>
-  </si>
-  <si>
-    <t>func_unlock_key</t>
-  </si>
-  <si>
-    <t>func_open_type</t>
-  </si>
-  <si>
-    <t>layout_slot</t>
-  </si>
-  <si>
-    <t>(list#sep=|),string</t>
-  </si>
-  <si>
-    <t>EFuncOpenType</t>
-  </si>
-  <si>
     <t>灯·A·地图</t>
   </si>
   <si>
@@ -282,13 +273,22 @@
     <t>需先解锁基础</t>
   </si>
   <si>
-    <t>rune_lady_initial</t>
-  </si>
-  <si>
-    <t>耐受核心·基础</t>
-  </si>
-  <si>
-    <t>核心槽基础效果</t>
+    <t>基础效果</t>
+  </si>
+  <si>
+    <t>rune_weiyi_regen_ooc</t>
+  </si>
+  <si>
+    <t>lady_up_1</t>
+  </si>
+  <si>
+    <t>淑女·α</t>
+  </si>
+  <si>
+    <t>威仪强化</t>
+  </si>
+  <si>
+    <t>rune_weiyi_more_layer</t>
   </si>
   <si>
     <t>rune_evil_hand_initial</t>
@@ -1268,21 +1268,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19.125" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="23.125" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="7" width="30.125" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="16.25" customWidth="1"/>
-    <col min="10" max="10" width="21.25" customWidth="1"/>
-    <col min="11" max="11" width="28.375" customWidth="1"/>
+    <col min="4" max="5" width="17.5" customWidth="1"/>
+    <col min="6" max="6" width="23.125" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="30.125" customWidth="1"/>
+    <col min="9" max="9" width="16.875" customWidth="1"/>
+    <col min="10" max="10" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1313,232 +1311,202 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
         <v>23</v>
       </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
         <v>33</v>
       </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" t="s">
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="H7" t="s">
+      <c r="C9" t="s">
         <v>36</v>
       </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="D9" t="s">
         <v>37</v>
       </c>
-      <c r="K7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" t="s">
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
+      <c r="H9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" t="s">
+      <c r="I9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="G9" t="s">
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
         <v>42</v>
       </c>
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="H10" t="s">
         <v>43</v>
       </c>
-      <c r="K9">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
-      </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1518,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -1570,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1579,127 +1547,127 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" t="s">
+      <c r="L1" t="s">
         <v>50</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
         <v>51</v>
-      </c>
-      <c r="H1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L2" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
         <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>61</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1710,28 +1678,28 @@
     </row>
     <row r="5" spans="1:13">
       <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
         <v>62</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
         <v>63</v>
       </c>
-      <c r="D5" t="s">
+      <c r="J5" t="s">
         <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" t="s">
-        <v>67</v>
       </c>
       <c r="L5">
         <v>2</v>
@@ -1742,22 +1710,22 @@
     </row>
     <row r="6" spans="1:13">
       <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
         <v>68</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" t="s">
         <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
-        <v>72</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -1768,25 +1736,25 @@
     </row>
     <row r="7" spans="1:13">
       <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" t="s">
         <v>73</v>
       </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>76</v>
-      </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -1797,22 +1765,22 @@
     </row>
     <row r="9" spans="1:13">
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
         <v>77</v>
       </c>
-      <c r="E9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" t="s">
-        <v>80</v>
-      </c>
       <c r="J9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -1823,22 +1791,22 @@
     </row>
     <row r="10" spans="1:13">
       <c r="B10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -1849,19 +1817,22 @@
     </row>
     <row r="12" spans="1:13">
       <c r="B12" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>82</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L12">
         <v>1</v>
@@ -1872,47 +1843,64 @@
     </row>
     <row r="13" spans="1:13">
       <c r="B13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="B15" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>88</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E15" t="s">
         <v>89</v>
       </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13">
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15">
         <v>1</v>
       </c>
-      <c r="M13">
+      <c r="M15">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="B14" t="s">
+    <row r="16" spans="1:13">
+      <c r="B16" t="s">
         <v>90</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>91</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E16" t="s">
         <v>92</v>
       </c>
-      <c r="F14" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L14">
+      <c r="F16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16">
         <v>1</v>
       </c>
-      <c r="M14">
+      <c r="M16">
         <v>17</v>
       </c>
     </row>

--- a/Config/Datas/rune.xlsx
+++ b/Config/Datas/rune.xlsx
@@ -1788,6 +1788,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
@@ -1824,7 +1825,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>8,None,8</t>
         </is>
       </c>
     </row>
@@ -1863,6 +1864,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
@@ -1968,6 +1970,7 @@
         <v>3</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
